--- a/output/yearly_total_coral_cover_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_10_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.275090418556838</v>
+        <v>1.262150983814865</v>
       </c>
       <c r="C3" t="n">
-        <v>4.652548403627896</v>
+        <v>4.684042869980133</v>
       </c>
       <c r="D3" t="n">
-        <v>6.070200145416402</v>
+        <v>6.056220058107928</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99783896760114</v>
+        <v>12.00241391190293</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.428244609958723</v>
+        <v>1.40275765486688</v>
       </c>
       <c r="C4" t="n">
-        <v>5.173574967143908</v>
+        <v>5.285038493403262</v>
       </c>
       <c r="D4" t="n">
-        <v>6.327820525869607</v>
+        <v>6.273893032158905</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92964010297224</v>
+        <v>12.96168918042905</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.630579165668817</v>
+        <v>1.590821222173372</v>
       </c>
       <c r="C5" t="n">
-        <v>5.828497939739259</v>
+        <v>6.069163906669006</v>
       </c>
       <c r="D5" t="n">
-        <v>6.67109176520075</v>
+        <v>6.492883452673134</v>
       </c>
       <c r="E5" t="n">
-        <v>14.13016887060883</v>
+        <v>14.15286858151551</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.852814202383267</v>
+        <v>1.817557494654839</v>
       </c>
       <c r="C6" t="n">
-        <v>6.635011679626413</v>
+        <v>7.02832499732771</v>
       </c>
       <c r="D6" t="n">
-        <v>7.033773408870312</v>
+        <v>6.793693833987304</v>
       </c>
       <c r="E6" t="n">
-        <v>15.52159929087999</v>
+        <v>15.63957632596985</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.102265119922172</v>
+        <v>2.085411279524735</v>
       </c>
       <c r="C7" t="n">
-        <v>7.570551746292687</v>
+        <v>8.145774847059455</v>
       </c>
       <c r="D7" t="n">
-        <v>7.402230319009734</v>
+        <v>7.141956835206009</v>
       </c>
       <c r="E7" t="n">
-        <v>17.07504718522459</v>
+        <v>17.3731429617902</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.297315712515623</v>
+        <v>1.315078489924639</v>
       </c>
       <c r="C8" t="n">
-        <v>5.174680479071887</v>
+        <v>5.749261360259185</v>
       </c>
       <c r="D8" t="n">
-        <v>5.575426779541952</v>
+        <v>5.333108753340726</v>
       </c>
       <c r="E8" t="n">
-        <v>12.04742297112946</v>
+        <v>12.39744860352455</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.616156223140202</v>
+        <v>1.6572422797752</v>
       </c>
       <c r="C9" t="n">
-        <v>6.343043264151562</v>
+        <v>7.10949649873823</v>
       </c>
       <c r="D9" t="n">
-        <v>5.989993628351624</v>
+        <v>5.815406916145355</v>
       </c>
       <c r="E9" t="n">
-        <v>13.94919311564339</v>
+        <v>14.58214569465878</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.946530105883005</v>
+        <v>2.013449229205111</v>
       </c>
       <c r="C10" t="n">
-        <v>7.643860089647732</v>
+        <v>8.610522422637121</v>
       </c>
       <c r="D10" t="n">
-        <v>6.513551791485023</v>
+        <v>6.342530459676901</v>
       </c>
       <c r="E10" t="n">
-        <v>16.10394198701576</v>
+        <v>16.96650211151913</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.295592925247603</v>
+        <v>2.376743859673306</v>
       </c>
       <c r="C11" t="n">
-        <v>9.105101276339573</v>
+        <v>10.25350155108183</v>
       </c>
       <c r="D11" t="n">
-        <v>6.942037912338034</v>
+        <v>6.858638114054929</v>
       </c>
       <c r="E11" t="n">
-        <v>18.34273211392521</v>
+        <v>19.48888352481007</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.647081390837757</v>
+        <v>2.73621066737674</v>
       </c>
       <c r="C12" t="n">
-        <v>10.70181098877924</v>
+        <v>11.96788173329088</v>
       </c>
       <c r="D12" t="n">
-        <v>7.412169969971051</v>
+        <v>7.300338723313406</v>
       </c>
       <c r="E12" t="n">
-        <v>20.76106234958805</v>
+        <v>22.00443112398102</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.004684447521228</v>
+        <v>3.067201073371016</v>
       </c>
       <c r="C13" t="n">
-        <v>12.38493537483042</v>
+        <v>13.68803929999806</v>
       </c>
       <c r="D13" t="n">
-        <v>7.826733774292451</v>
+        <v>7.796251627499036</v>
       </c>
       <c r="E13" t="n">
-        <v>23.2163535966441</v>
+        <v>24.55149200086811</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.752252754970835</v>
+        <v>1.758221781012655</v>
       </c>
       <c r="C14" t="n">
-        <v>8.789803180616627</v>
+        <v>9.609965030221456</v>
       </c>
       <c r="D14" t="n">
-        <v>5.932907543781366</v>
+        <v>5.981906571700325</v>
       </c>
       <c r="E14" t="n">
-        <v>16.47496347936883</v>
+        <v>17.35009338293444</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.801340140183175</v>
+        <v>1.793986849878366</v>
       </c>
       <c r="C15" t="n">
-        <v>9.603377503125961</v>
+        <v>10.37094712821429</v>
       </c>
       <c r="D15" t="n">
-        <v>5.911132379701173</v>
+        <v>5.992234557549002</v>
       </c>
       <c r="E15" t="n">
-        <v>17.31585002301031</v>
+        <v>18.15716853564166</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.095137958156076</v>
+        <v>2.06596041638586</v>
       </c>
       <c r="C16" t="n">
-        <v>11.47445118274178</v>
+        <v>12.19696840568223</v>
       </c>
       <c r="D16" t="n">
-        <v>6.299688486087976</v>
+        <v>6.435896162575179</v>
       </c>
       <c r="E16" t="n">
-        <v>19.86927762698584</v>
+        <v>20.69882498464327</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.679220543251914</v>
+        <v>1.650249168499591</v>
       </c>
       <c r="C17" t="n">
-        <v>10.69285238295977</v>
+        <v>11.14383782585963</v>
       </c>
       <c r="D17" t="n">
-        <v>5.79827066362096</v>
+        <v>5.977390532260791</v>
       </c>
       <c r="E17" t="n">
-        <v>18.17034358983265</v>
+        <v>18.77147752662001</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.912326718148277</v>
+        <v>1.871613640853162</v>
       </c>
       <c r="C18" t="n">
-        <v>12.57519652622035</v>
+        <v>12.95284541561297</v>
       </c>
       <c r="D18" t="n">
-        <v>6.203634290704468</v>
+        <v>6.40221239884247</v>
       </c>
       <c r="E18" t="n">
-        <v>20.6911575350731</v>
+        <v>21.2266714553086</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.913220108559142</v>
+        <v>1.868825477373101</v>
       </c>
       <c r="C19" t="n">
-        <v>13.52715800512031</v>
+        <v>13.78085142937474</v>
       </c>
       <c r="D19" t="n">
-        <v>6.263648527865075</v>
+        <v>6.492847346898537</v>
       </c>
       <c r="E19" t="n">
-        <v>21.70402664154453</v>
+        <v>22.14252425364637</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.129724929776691</v>
+        <v>2.066647639778834</v>
       </c>
       <c r="C20" t="n">
-        <v>15.56807403757084</v>
+        <v>15.76943049171186</v>
       </c>
       <c r="D20" t="n">
-        <v>6.683178774320864</v>
+        <v>6.912544490464048</v>
       </c>
       <c r="E20" t="n">
-        <v>24.38097774166839</v>
+        <v>24.74862262195474</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.266925777376424</v>
+        <v>1.219242291381156</v>
       </c>
       <c r="C21" t="n">
-        <v>11.45392283824599</v>
+        <v>11.52893818032748</v>
       </c>
       <c r="D21" t="n">
-        <v>5.556466204064971</v>
+        <v>5.779106948434062</v>
       </c>
       <c r="E21" t="n">
-        <v>18.27731481968738</v>
+        <v>18.5272874201427</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_10_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.262150983814865</v>
+        <v>1.244273358120531</v>
       </c>
       <c r="C3" t="n">
-        <v>4.684042869980133</v>
+        <v>4.65945008998875</v>
       </c>
       <c r="D3" t="n">
-        <v>6.056220058107928</v>
+        <v>6.055837176503271</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00241391190293</v>
+        <v>11.95956062461255</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.40275765486688</v>
+        <v>1.357545711794943</v>
       </c>
       <c r="C4" t="n">
-        <v>5.285038493403262</v>
+        <v>5.215147116225333</v>
       </c>
       <c r="D4" t="n">
-        <v>6.273893032158905</v>
+        <v>6.277104212585401</v>
       </c>
       <c r="E4" t="n">
-        <v>12.96168918042905</v>
+        <v>12.84979704060568</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.590821222173372</v>
+        <v>1.521019198154024</v>
       </c>
       <c r="C5" t="n">
-        <v>6.069163906669006</v>
+        <v>5.924953729254847</v>
       </c>
       <c r="D5" t="n">
-        <v>6.492883452673134</v>
+        <v>6.557498519654612</v>
       </c>
       <c r="E5" t="n">
-        <v>14.15286858151551</v>
+        <v>14.00347144706348</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.817557494654839</v>
+        <v>1.707555086659463</v>
       </c>
       <c r="C6" t="n">
-        <v>7.02832499732771</v>
+        <v>6.789407907373765</v>
       </c>
       <c r="D6" t="n">
-        <v>6.793693833987304</v>
+        <v>6.840080120317076</v>
       </c>
       <c r="E6" t="n">
-        <v>15.63957632596985</v>
+        <v>15.3370431143503</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.085411279524735</v>
+        <v>1.918581922749982</v>
       </c>
       <c r="C7" t="n">
-        <v>8.145774847059455</v>
+        <v>7.796451002286407</v>
       </c>
       <c r="D7" t="n">
-        <v>7.141956835206009</v>
+        <v>7.197035900858078</v>
       </c>
       <c r="E7" t="n">
-        <v>17.3731429617902</v>
+        <v>16.91206882589447</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.315078489924639</v>
+        <v>1.15756203390721</v>
       </c>
       <c r="C8" t="n">
-        <v>5.749261360259185</v>
+        <v>5.416014361478545</v>
       </c>
       <c r="D8" t="n">
-        <v>5.333108753340726</v>
+        <v>5.417902091806225</v>
       </c>
       <c r="E8" t="n">
-        <v>12.39744860352455</v>
+        <v>11.99147848719198</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.6572422797752</v>
+        <v>1.430934200941754</v>
       </c>
       <c r="C9" t="n">
-        <v>7.10949649873823</v>
+        <v>6.707717742354895</v>
       </c>
       <c r="D9" t="n">
-        <v>5.815406916145355</v>
+        <v>5.924001037685974</v>
       </c>
       <c r="E9" t="n">
-        <v>14.58214569465878</v>
+        <v>14.06265298098262</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.013449229205111</v>
+        <v>1.7153143128452</v>
       </c>
       <c r="C10" t="n">
-        <v>8.610522422637121</v>
+        <v>8.187475569078059</v>
       </c>
       <c r="D10" t="n">
-        <v>6.342530459676901</v>
+        <v>6.415470716834974</v>
       </c>
       <c r="E10" t="n">
-        <v>16.96650211151913</v>
+        <v>16.31826059875823</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.376743859673306</v>
+        <v>1.999015226606145</v>
       </c>
       <c r="C11" t="n">
-        <v>10.25350155108183</v>
+        <v>9.80000664504788</v>
       </c>
       <c r="D11" t="n">
-        <v>6.858638114054929</v>
+        <v>6.947615182273489</v>
       </c>
       <c r="E11" t="n">
-        <v>19.48888352481007</v>
+        <v>18.74663705392751</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.73621066737674</v>
+        <v>2.282849787160616</v>
       </c>
       <c r="C12" t="n">
-        <v>11.96788173329088</v>
+        <v>11.48482150561826</v>
       </c>
       <c r="D12" t="n">
-        <v>7.300338723313406</v>
+        <v>7.451317443649081</v>
       </c>
       <c r="E12" t="n">
-        <v>22.00443112398102</v>
+        <v>21.21898873642796</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.067201073371016</v>
+        <v>2.552218407421018</v>
       </c>
       <c r="C13" t="n">
-        <v>13.68803929999806</v>
+        <v>13.19947236137275</v>
       </c>
       <c r="D13" t="n">
-        <v>7.796251627499036</v>
+        <v>8.022677986276088</v>
       </c>
       <c r="E13" t="n">
-        <v>24.55149200086811</v>
+        <v>23.77436875506986</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.758221781012655</v>
+        <v>1.479729409748963</v>
       </c>
       <c r="C14" t="n">
-        <v>9.609965030221456</v>
+        <v>9.223097529885957</v>
       </c>
       <c r="D14" t="n">
-        <v>5.981906571700325</v>
+        <v>6.136688914751877</v>
       </c>
       <c r="E14" t="n">
-        <v>17.35009338293444</v>
+        <v>16.8395158543868</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.793986849878366</v>
+        <v>1.491873628850496</v>
       </c>
       <c r="C15" t="n">
-        <v>10.37094712821429</v>
+        <v>9.974762842165486</v>
       </c>
       <c r="D15" t="n">
-        <v>5.992234557549002</v>
+        <v>6.181672594560466</v>
       </c>
       <c r="E15" t="n">
-        <v>18.15716853564166</v>
+        <v>17.64830906557645</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.06596041638586</v>
+        <v>1.7044612767281</v>
       </c>
       <c r="C16" t="n">
-        <v>12.19696840568223</v>
+        <v>11.75904020724885</v>
       </c>
       <c r="D16" t="n">
-        <v>6.435896162575179</v>
+        <v>6.690198270406229</v>
       </c>
       <c r="E16" t="n">
-        <v>20.69882498464327</v>
+        <v>20.15369975438318</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.650249168499591</v>
+        <v>1.346653508438307</v>
       </c>
       <c r="C17" t="n">
-        <v>11.14383782585963</v>
+        <v>10.77994322180351</v>
       </c>
       <c r="D17" t="n">
-        <v>5.977390532260791</v>
+        <v>6.238397976911846</v>
       </c>
       <c r="E17" t="n">
-        <v>18.77147752662001</v>
+        <v>18.36499470715366</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.871613640853162</v>
+        <v>1.518204102278395</v>
       </c>
       <c r="C18" t="n">
-        <v>12.95284541561297</v>
+        <v>12.58042924148399</v>
       </c>
       <c r="D18" t="n">
-        <v>6.40221239884247</v>
+        <v>6.712032339348679</v>
       </c>
       <c r="E18" t="n">
-        <v>21.2266714553086</v>
+        <v>20.81066568311106</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.868825477373101</v>
+        <v>1.50597152588348</v>
       </c>
       <c r="C19" t="n">
-        <v>13.78085142937474</v>
+        <v>13.46378619081118</v>
       </c>
       <c r="D19" t="n">
-        <v>6.492847346898537</v>
+        <v>6.841937195574618</v>
       </c>
       <c r="E19" t="n">
-        <v>22.14252425364637</v>
+        <v>21.81169491226928</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.066647639778834</v>
+        <v>1.666978149379957</v>
       </c>
       <c r="C20" t="n">
-        <v>15.76943049171186</v>
+        <v>15.42951998407049</v>
       </c>
       <c r="D20" t="n">
-        <v>6.912544490464048</v>
+        <v>7.288769845685509</v>
       </c>
       <c r="E20" t="n">
-        <v>24.74862262195474</v>
+        <v>24.38526797913595</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.219242291381156</v>
+        <v>0.9878443574901832</v>
       </c>
       <c r="C21" t="n">
-        <v>11.52893818032748</v>
+        <v>11.30303803358029</v>
       </c>
       <c r="D21" t="n">
-        <v>5.779106948434062</v>
+        <v>6.11541444200085</v>
       </c>
       <c r="E21" t="n">
-        <v>18.5272874201427</v>
+        <v>18.40629683307133</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_10_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.244273358120531</v>
+        <v>2.629326040874379</v>
       </c>
       <c r="C3" t="n">
-        <v>4.65945008998875</v>
+        <v>7.747164653108936</v>
       </c>
       <c r="D3" t="n">
-        <v>6.055837176503271</v>
+        <v>8.233886348144294</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95956062461255</v>
+        <v>18.61037704212761</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.357545711794943</v>
+        <v>1.16008968911978</v>
       </c>
       <c r="C4" t="n">
-        <v>5.215147116225333</v>
+        <v>4.589627933445843</v>
       </c>
       <c r="D4" t="n">
-        <v>6.277104212585401</v>
+        <v>5.820123559480323</v>
       </c>
       <c r="E4" t="n">
-        <v>12.84979704060568</v>
+        <v>11.56984118204594</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.521019198154024</v>
+        <v>1.336701913846542</v>
       </c>
       <c r="C5" t="n">
-        <v>5.924953729254847</v>
+        <v>5.323358977354077</v>
       </c>
       <c r="D5" t="n">
-        <v>6.557498519654612</v>
+        <v>6.193184844067711</v>
       </c>
       <c r="E5" t="n">
-        <v>14.00347144706348</v>
+        <v>12.85324573526833</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.707555086659463</v>
+        <v>1.521822982020566</v>
       </c>
       <c r="C6" t="n">
-        <v>6.789407907373765</v>
+        <v>6.228419767450617</v>
       </c>
       <c r="D6" t="n">
-        <v>6.840080120317076</v>
+        <v>6.606731088622923</v>
       </c>
       <c r="E6" t="n">
-        <v>15.3370431143503</v>
+        <v>14.35697383809411</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.918581922749982</v>
+        <v>1.715870580694872</v>
       </c>
       <c r="C7" t="n">
-        <v>7.796451002286407</v>
+        <v>7.246477145081914</v>
       </c>
       <c r="D7" t="n">
-        <v>7.197035900858078</v>
+        <v>7.017065261843057</v>
       </c>
       <c r="E7" t="n">
-        <v>16.91206882589447</v>
+        <v>15.97941298761984</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.15756203390721</v>
+        <v>1.910380163125289</v>
       </c>
       <c r="C8" t="n">
-        <v>5.416014361478545</v>
+        <v>8.351338479097359</v>
       </c>
       <c r="D8" t="n">
-        <v>5.417902091806225</v>
+        <v>7.46465172762844</v>
       </c>
       <c r="E8" t="n">
-        <v>11.99147848719198</v>
+        <v>17.72637036985109</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.430934200941754</v>
+        <v>2.084441740483088</v>
       </c>
       <c r="C9" t="n">
-        <v>6.707717742354895</v>
+        <v>9.532596137817988</v>
       </c>
       <c r="D9" t="n">
-        <v>5.924001037685974</v>
+        <v>7.90639368485669</v>
       </c>
       <c r="E9" t="n">
-        <v>14.06265298098262</v>
+        <v>19.52343156315776</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.7153143128452</v>
+        <v>1.255380424374481</v>
       </c>
       <c r="C10" t="n">
-        <v>8.187475569078059</v>
+        <v>6.904278174794289</v>
       </c>
       <c r="D10" t="n">
-        <v>6.415470716834974</v>
+        <v>6.223121982633767</v>
       </c>
       <c r="E10" t="n">
-        <v>16.31826059875823</v>
+        <v>14.38278058180254</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.999015226606145</v>
+        <v>1.205713808016635</v>
       </c>
       <c r="C11" t="n">
-        <v>9.80000664504788</v>
+        <v>7.205920156924121</v>
       </c>
       <c r="D11" t="n">
-        <v>6.947615182273489</v>
+        <v>6.116239110072416</v>
       </c>
       <c r="E11" t="n">
-        <v>18.74663705392751</v>
+        <v>14.52787307501317</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.282849787160616</v>
+        <v>1.324554367615712</v>
       </c>
       <c r="C12" t="n">
-        <v>11.48482150561826</v>
+        <v>8.377694946804944</v>
       </c>
       <c r="D12" t="n">
-        <v>7.451317443649081</v>
+        <v>6.514858130427749</v>
       </c>
       <c r="E12" t="n">
-        <v>21.21898873642796</v>
+        <v>16.21710744484841</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.552218407421018</v>
+        <v>1.050911830010998</v>
       </c>
       <c r="C13" t="n">
-        <v>13.19947236137275</v>
+        <v>7.839932824326713</v>
       </c>
       <c r="D13" t="n">
-        <v>8.022677986276088</v>
+        <v>5.974209669699031</v>
       </c>
       <c r="E13" t="n">
-        <v>23.77436875506986</v>
+        <v>14.86505432403674</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.479729409748963</v>
+        <v>1.151452612402914</v>
       </c>
       <c r="C14" t="n">
-        <v>9.223097529885957</v>
+        <v>9.050810625267685</v>
       </c>
       <c r="D14" t="n">
-        <v>6.136688914751877</v>
+        <v>6.391295364371246</v>
       </c>
       <c r="E14" t="n">
-        <v>16.8395158543868</v>
+        <v>16.59355860204185</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.491873628850496</v>
+        <v>1.127635413097887</v>
       </c>
       <c r="C15" t="n">
-        <v>9.974762842165486</v>
+        <v>9.657844865757571</v>
       </c>
       <c r="D15" t="n">
-        <v>6.181672594560466</v>
+        <v>6.480379151054601</v>
       </c>
       <c r="E15" t="n">
-        <v>17.64830906557645</v>
+        <v>17.26585942991006</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.7044612767281</v>
+        <v>1.247536260217549</v>
       </c>
       <c r="C16" t="n">
-        <v>11.75904020724885</v>
+        <v>11.18608242957337</v>
       </c>
       <c r="D16" t="n">
-        <v>6.690198270406229</v>
+        <v>6.92086971099606</v>
       </c>
       <c r="E16" t="n">
-        <v>20.15369975438318</v>
+        <v>19.35448840078698</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.346653508438307</v>
+        <v>0.7511940733814895</v>
       </c>
       <c r="C17" t="n">
-        <v>10.77994322180351</v>
+        <v>8.347653467054991</v>
       </c>
       <c r="D17" t="n">
-        <v>6.238397976911846</v>
+        <v>5.7781448356839</v>
       </c>
       <c r="E17" t="n">
-        <v>18.36499470715366</v>
+        <v>14.87699237612038</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.518204102278395</v>
+        <v>0.6093609825489528</v>
       </c>
       <c r="C18" t="n">
-        <v>12.58042924148399</v>
+        <v>7.249686469579444</v>
       </c>
       <c r="D18" t="n">
-        <v>6.712032339348679</v>
+        <v>5.291512133642841</v>
       </c>
       <c r="E18" t="n">
-        <v>20.81066568311106</v>
+        <v>13.15055958577124</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.50597152588348</v>
+        <v>0.7266896506834891</v>
       </c>
       <c r="C19" t="n">
-        <v>13.46378619081118</v>
+        <v>8.94140466110642</v>
       </c>
       <c r="D19" t="n">
-        <v>6.841937195574618</v>
+        <v>5.788659353596383</v>
       </c>
       <c r="E19" t="n">
-        <v>21.81169491226928</v>
+        <v>15.45675366538629</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.666978149379957</v>
+        <v>0.8388837783248148</v>
       </c>
       <c r="C20" t="n">
-        <v>15.42951998407049</v>
+        <v>10.7768899864433</v>
       </c>
       <c r="D20" t="n">
-        <v>7.288769845685509</v>
+        <v>6.348550069328339</v>
       </c>
       <c r="E20" t="n">
-        <v>24.38526797913595</v>
+        <v>17.96432383409645</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9878443574901832</v>
+        <v>0.9419476523166448</v>
       </c>
       <c r="C21" t="n">
-        <v>11.30303803358029</v>
+        <v>12.64778695147236</v>
       </c>
       <c r="D21" t="n">
-        <v>6.11541444200085</v>
+        <v>6.877083763386652</v>
       </c>
       <c r="E21" t="n">
-        <v>18.40629683307133</v>
+        <v>20.46681836717566</v>
       </c>
     </row>
   </sheetData>
